--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PALMER BASKET MALLORCA PALMA.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PALMER BASKET MALLORCA PALMA.xlsx
@@ -565,13 +565,13 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>30.9217</v>
+        <v>42.2978</v>
       </c>
       <c r="E2" t="n">
-        <v>29.0328</v>
+        <v>37.8402</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8888</v>
+        <v>4.457599999999999</v>
       </c>
       <c r="G2" t="n">
         <v>33.3329</v>
@@ -610,13 +610,13 @@
         <v>32.1912</v>
       </c>
       <c r="S2" t="n">
-        <v>-18.9612</v>
+        <v>-7.5852</v>
       </c>
       <c r="T2" t="n">
-        <v>-13.496</v>
+        <v>-4.688800000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-5.4653</v>
+        <v>-2.8962</v>
       </c>
       <c r="V2" t="n">
         <v>21.9877</v>
@@ -643,13 +643,13 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>26.4251</v>
+        <v>14.8208</v>
       </c>
       <c r="E3" t="n">
-        <v>20.3675</v>
+        <v>12.0867</v>
       </c>
       <c r="F3" t="n">
-        <v>6.057700000000001</v>
+        <v>2.734500000000001</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5680000000000002</v>
@@ -688,13 +688,13 @@
         <v>25.448</v>
       </c>
       <c r="S3" t="n">
-        <v>17.3354</v>
+        <v>5.731</v>
       </c>
       <c r="T3" t="n">
-        <v>11.314</v>
+        <v>3.0333</v>
       </c>
       <c r="U3" t="n">
-        <v>6.0212</v>
+        <v>2.6976</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3472999999999998</v>
@@ -721,13 +721,13 @@
         <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>14.9629</v>
+        <v>10.9548</v>
       </c>
       <c r="E4" t="n">
-        <v>18.9794</v>
+        <v>13.5428</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.0163</v>
+        <v>-2.588</v>
       </c>
       <c r="G4" t="n">
         <v>7.5883</v>
@@ -766,13 +766,13 @@
         <v>35.4532</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.739099999999999</v>
+        <v>-5.746799999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>3.9358</v>
+        <v>-1.5006</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.6749</v>
+        <v>-4.2464</v>
       </c>
       <c r="V4" t="n">
         <v>0.6304</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>M. FRIERSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2254999999999999</v>
+        <v>1.0617</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1545</v>
+        <v>2.7691</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3800000000000001</v>
+        <v>-1.7074</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8686</v>
+        <v>0.1743000000000006</v>
       </c>
       <c r="H5" t="n">
-        <v>0.365</v>
+        <v>2.1465</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5036</v>
+        <v>-1.9721</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7913</v>
+        <v>1.9591</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7149</v>
+        <v>1.0497</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0764</v>
+        <v>0.9093999999999998</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07719999999999999</v>
+        <v>-1.7847</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3499</v>
+        <v>1.0969</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4272</v>
+        <v>-2.8816</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.305</v>
+        <v>5.8725</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3926</v>
+        <v>-0.435</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>6.3075</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1664</v>
+        <v>-3.8346</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7557</v>
+        <v>-1.2101</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5892999999999999</v>
+        <v>-2.6246</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9554</v>
+        <v>-1.1506</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9554</v>
+        <v>-3.605799999999999</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0656</v>
+        <v>-0.8981999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5629</v>
+        <v>-1.0531</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5027</v>
+        <v>0.1549</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1643</v>
@@ -922,13 +922,13 @@
         <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.139</v>
+        <v>-0.9715</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8892</v>
+        <v>0.399</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.0283</v>
+        <v>-1.3706</v>
       </c>
       <c r="V6" t="n">
         <v>1.3252</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. FRIERSON</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6118</v>
+        <v>-1.4291</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9126000000000003</v>
+        <v>-1.0749</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5243</v>
+        <v>-0.3542999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1743000000000006</v>
+        <v>0.8686</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1465</v>
+        <v>0.365</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.9721</v>
+        <v>0.5036</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9591</v>
+        <v>0.7913</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0497</v>
+        <v>0.7149</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9093999999999998</v>
+        <v>0.0764</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7847</v>
+        <v>0.07719999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>1.0969</v>
+        <v>-0.3499</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.8816</v>
+        <v>0.4272</v>
       </c>
       <c r="P7" t="n">
-        <v>5.8725</v>
+        <v>-1.305</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.435</v>
+        <v>-2.3926</v>
       </c>
       <c r="R7" t="n">
-        <v>6.3075</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>-6.5081</v>
+        <v>-0.03720000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.0667</v>
+        <v>0.5264</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.4415</v>
+        <v>-0.5636</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1506</v>
+        <v>-0.9554</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.605799999999999</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0084</v>
+        <v>-4.202</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.7411</v>
+        <v>-4.1197</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2672999999999999</v>
+        <v>-0.08230000000000004</v>
       </c>
       <c r="G8" t="n">
         <v>-4.0501</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1713</v>
+        <v>-0.0222</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1971</v>
+        <v>-0.1815</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.02589999999999999</v>
+        <v>0.1593</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3473</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.298800000000004</v>
+        <v>-7.404300000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.083600000000001</v>
+        <v>-7.942500000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2150000000000003</v>
+        <v>0.5381</v>
       </c>
       <c r="G9" t="n">
-        <v>-33.7403</v>
+        <v>-5.0199</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.039899999999999</v>
+        <v>-4.9657</v>
       </c>
       <c r="I9" t="n">
-        <v>-25.7003</v>
+        <v>-0.05419999999999991</v>
       </c>
       <c r="J9" t="n">
-        <v>-12.1649</v>
+        <v>-0.2626999999999997</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6738000000000003</v>
+        <v>-3.9396</v>
       </c>
       <c r="L9" t="n">
-        <v>-11.491</v>
+        <v>3.6767</v>
       </c>
       <c r="M9" t="n">
-        <v>-21.5754</v>
+        <v>-4.7571</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.3659</v>
+        <v>-1.0263</v>
       </c>
       <c r="O9" t="n">
-        <v>-14.2092</v>
+        <v>-3.7311</v>
       </c>
       <c r="P9" t="n">
-        <v>19.1403</v>
+        <v>-4.3501</v>
       </c>
       <c r="Q9" t="n">
-        <v>-21.5331</v>
+        <v>-11.7452</v>
       </c>
       <c r="R9" t="n">
-        <v>40.6738</v>
+        <v>7.395099999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>8.214600000000001</v>
+        <v>-1.0545</v>
       </c>
       <c r="T9" t="n">
-        <v>10.7591</v>
+        <v>-0.8447</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.5443</v>
+        <v>-0.2097</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.9138</v>
+        <v>3.0201</v>
       </c>
       <c r="W9" t="n">
-        <v>14.8552</v>
+        <v>4.910299999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-16.7692</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>D. AGBELESE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.0268</v>
+        <v>-12.2658</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.154</v>
+        <v>-9.4269</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1269999999999998</v>
+        <v>-2.8391</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.0199</v>
+        <v>-1.923</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.9657</v>
+        <v>-0.3315999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05419999999999991</v>
+        <v>-1.5913</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2626999999999997</v>
+        <v>0.5126999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.9396</v>
+        <v>0.09199999999999989</v>
       </c>
       <c r="L10" t="n">
-        <v>3.6767</v>
+        <v>0.4206</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.7571</v>
+        <v>-2.4357</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0263</v>
+        <v>-0.4236000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.7311</v>
+        <v>-2.0122</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.3501</v>
+        <v>-4.7851</v>
       </c>
       <c r="Q10" t="n">
-        <v>-11.7452</v>
+        <v>-8.9177</v>
       </c>
       <c r="R10" t="n">
-        <v>7.395099999999999</v>
+        <v>4.1326</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.677</v>
+        <v>-0.8427</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.056</v>
+        <v>-1.2377</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6208</v>
+        <v>0.395</v>
       </c>
       <c r="V10" t="n">
-        <v>3.0201</v>
+        <v>-4.7151</v>
       </c>
       <c r="W10" t="n">
-        <v>4.910299999999999</v>
+        <v>0.2158999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8902</v>
+        <v>-4.930899999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. AGBELESE</t>
+          <t>A. CHAPELA LAGE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.9662</v>
+        <v>-15.386</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.5639</v>
+        <v>-17.3782</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4024</v>
+        <v>1.9925</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.923</v>
+        <v>-10.6103</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3315999999999999</v>
+        <v>-9.413600000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5913</v>
+        <v>-1.1967</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5126999999999999</v>
+        <v>-0.7638000000000003</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09199999999999989</v>
+        <v>-4.7092</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4206</v>
+        <v>3.9454</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4357</v>
+        <v>-9.8467</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4236000000000001</v>
+        <v>-4.7044</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0122</v>
+        <v>-5.1426</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.7851</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.9177</v>
+        <v>-16.0954</v>
       </c>
       <c r="R11" t="n">
-        <v>4.1326</v>
+        <v>13.2677</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.543</v>
+        <v>-4.0128</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3748</v>
+        <v>-2.2351</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8317</v>
+        <v>-1.7778</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.7151</v>
+        <v>2.0647</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2158999999999999</v>
+        <v>1.7156</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.930899999999999</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>I. MASSOUD RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.2667</v>
+        <v>-15.8194</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.5993</v>
+        <v>-9.010199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.6674</v>
+        <v>-6.809</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.7254</v>
+        <v>-8.898200000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.0513</v>
+        <v>-5.1228</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.674200000000001</v>
+        <v>-3.775399999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>17.1201</v>
+        <v>0.7963999999999998</v>
       </c>
       <c r="K12" t="n">
-        <v>8.2364</v>
+        <v>-0.5555000000000002</v>
       </c>
       <c r="L12" t="n">
-        <v>8.8832</v>
+        <v>1.3515</v>
       </c>
       <c r="M12" t="n">
-        <v>-30.8458</v>
+        <v>-9.6942</v>
       </c>
       <c r="N12" t="n">
-        <v>-13.2878</v>
+        <v>-4.5671</v>
       </c>
       <c r="O12" t="n">
-        <v>-17.558</v>
+        <v>-5.127</v>
       </c>
       <c r="P12" t="n">
-        <v>9.5702</v>
+        <v>2.3925</v>
       </c>
       <c r="Q12" t="n">
-        <v>-30.0156</v>
+        <v>-7.395099999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>39.5861</v>
+        <v>9.787699999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>4.9241</v>
+        <v>-7.186999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>6.5854</v>
+        <v>-3.5414</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.6613</v>
+        <v>-3.6456</v>
       </c>
       <c r="V12" t="n">
-        <v>-17.0357</v>
+        <v>-2.1268</v>
       </c>
       <c r="W12" t="n">
-        <v>-5.2891</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.7467</v>
+        <v>-3.2567</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. MASSOUD RODRÍGUEZ</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.1156</v>
+        <v>-16.9451</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.159</v>
+        <v>-15.9035</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.9566</v>
+        <v>-1.0417</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.898200000000001</v>
+        <v>-33.7403</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.1228</v>
+        <v>-8.039899999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.775399999999999</v>
+        <v>-25.7003</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7963999999999998</v>
+        <v>-12.1649</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5555000000000002</v>
+        <v>-0.6738000000000003</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3515</v>
+        <v>-11.491</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.6942</v>
+        <v>-21.5754</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.5671</v>
+        <v>-7.3659</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.127</v>
+        <v>-14.2092</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3925</v>
+        <v>19.1403</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.395099999999999</v>
+        <v>-21.5331</v>
       </c>
       <c r="R13" t="n">
-        <v>9.787699999999999</v>
+        <v>40.6738</v>
       </c>
       <c r="S13" t="n">
-        <v>-11.4832</v>
+        <v>-0.4316000000000003</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.6901</v>
+        <v>2.9397</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.7934</v>
+        <v>-3.3712</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1268</v>
+        <v>-1.9138</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>14.8552</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.2567</v>
+        <v>-16.7692</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CHAPELA LAGE</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-20.4043</v>
+        <v>-21.4055</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.7444</v>
+        <v>-14.2079</v>
       </c>
       <c r="F14" t="n">
-        <v>1.34</v>
+        <v>-7.1979</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.6103</v>
+        <v>-17.747</v>
       </c>
       <c r="H14" t="n">
-        <v>-9.413600000000001</v>
+        <v>-4.448900000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1967</v>
+        <v>-13.2979</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7638000000000003</v>
+        <v>6.327800000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.7092</v>
+        <v>2.828</v>
       </c>
       <c r="L14" t="n">
-        <v>3.9454</v>
+        <v>3.4995</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.8467</v>
+        <v>-24.0748</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.7044</v>
+        <v>-7.2774</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.1426</v>
+        <v>-16.7972</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.8276</v>
+        <v>-2.610100000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.0954</v>
+        <v>-33.2784</v>
       </c>
       <c r="R14" t="n">
-        <v>13.2677</v>
+        <v>30.6681</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.0311</v>
+        <v>-2.7536</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.601</v>
+        <v>0.03500000000000014</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.4304</v>
+        <v>-2.7887</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0647</v>
+        <v>1.705</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7156</v>
+        <v>12.7076</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3491</v>
+        <v>-11.0028</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>-21.2704</v>
+        <v>-21.5839</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.416499999999999</v>
+        <v>-15.5399</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.8532</v>
+        <v>-6.0443</v>
       </c>
       <c r="G15" t="n">
-        <v>-34.7884</v>
+        <v>-13.7254</v>
       </c>
       <c r="H15" t="n">
-        <v>-9.2744</v>
+        <v>-5.0513</v>
       </c>
       <c r="I15" t="n">
-        <v>-25.5138</v>
+        <v>-8.674200000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.391300000000001</v>
+        <v>17.1201</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.6088</v>
+        <v>8.2364</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7827999999999993</v>
+        <v>8.8832</v>
       </c>
       <c r="M15" t="n">
-        <v>-32.3968</v>
+        <v>-30.8458</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.6658</v>
+        <v>-13.2878</v>
       </c>
       <c r="O15" t="n">
-        <v>-24.7311</v>
+        <v>-17.558</v>
       </c>
       <c r="P15" t="n">
-        <v>5.8724</v>
+        <v>9.5702</v>
       </c>
       <c r="Q15" t="n">
-        <v>-36.7584</v>
+        <v>-30.0156</v>
       </c>
       <c r="R15" t="n">
-        <v>42.6308</v>
+        <v>39.5861</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02150000000000074</v>
+        <v>-0.3926000000000002</v>
       </c>
       <c r="T15" t="n">
-        <v>3.9457</v>
+        <v>2.645</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.9238</v>
+        <v>-3.0375</v>
       </c>
       <c r="V15" t="n">
-        <v>7.623699999999999</v>
+        <v>-17.0357</v>
       </c>
       <c r="W15" t="n">
-        <v>27.7876</v>
+        <v>-5.2891</v>
       </c>
       <c r="X15" t="n">
-        <v>-20.1642</v>
+        <v>-11.7467</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>T. HOLLOWELL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>-24.2463</v>
+        <v>-23.1215</v>
       </c>
       <c r="E16" t="n">
-        <v>-13.8942</v>
+        <v>-9.621600000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-10.3521</v>
+        <v>-13.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-17.747</v>
+        <v>-16.2182</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.448900000000001</v>
+        <v>-11.4149</v>
       </c>
       <c r="I16" t="n">
-        <v>-13.2979</v>
+        <v>-4.8031</v>
       </c>
       <c r="J16" t="n">
-        <v>6.327800000000001</v>
+        <v>-4.0751</v>
       </c>
       <c r="K16" t="n">
-        <v>2.828</v>
+        <v>-3.2564</v>
       </c>
       <c r="L16" t="n">
-        <v>3.4995</v>
+        <v>-0.8188000000000003</v>
       </c>
       <c r="M16" t="n">
-        <v>-24.0748</v>
+        <v>-12.1429</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.2774</v>
+        <v>-8.1585</v>
       </c>
       <c r="O16" t="n">
-        <v>-16.7972</v>
+        <v>-3.9843</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.610100000000001</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q16" t="n">
-        <v>-33.2784</v>
+        <v>-8.2651</v>
       </c>
       <c r="R16" t="n">
-        <v>30.6681</v>
+        <v>6.307499999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.594599999999999</v>
+        <v>-3.0043</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3485999999999999</v>
+        <v>-1.4312</v>
       </c>
       <c r="U16" t="n">
-        <v>-5.9435</v>
+        <v>-1.5731</v>
       </c>
       <c r="V16" t="n">
-        <v>1.705</v>
+        <v>-1.9417</v>
       </c>
       <c r="W16" t="n">
-        <v>12.7076</v>
+        <v>4.1502</v>
       </c>
       <c r="X16" t="n">
-        <v>-11.0028</v>
+        <v>-6.0918</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. HOLLOWELL</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>-26.6887</v>
+        <v>-24.7178</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.3973</v>
+        <v>-13.1202</v>
       </c>
       <c r="F17" t="n">
-        <v>-14.2912</v>
+        <v>-11.5979</v>
       </c>
       <c r="G17" t="n">
-        <v>-16.2182</v>
+        <v>-34.7884</v>
       </c>
       <c r="H17" t="n">
-        <v>-11.4149</v>
+        <v>-9.2744</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.8031</v>
+        <v>-25.5138</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.0751</v>
+        <v>-2.391300000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.2564</v>
+        <v>-1.6088</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.8188000000000003</v>
+        <v>-0.7827999999999993</v>
       </c>
       <c r="M17" t="n">
-        <v>-12.1429</v>
+        <v>-32.3968</v>
       </c>
       <c r="N17" t="n">
-        <v>-8.1585</v>
+        <v>-7.6658</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.9843</v>
+        <v>-24.7311</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9576</v>
+        <v>5.8724</v>
       </c>
       <c r="Q17" t="n">
-        <v>-8.2651</v>
+        <v>-36.7584</v>
       </c>
       <c r="R17" t="n">
-        <v>6.307499999999999</v>
+        <v>42.6308</v>
       </c>
       <c r="S17" t="n">
-        <v>-6.5714</v>
+        <v>-3.425999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-4.2071</v>
+        <v>-1.7575</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.3642</v>
+        <v>-1.6682</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.9417</v>
+        <v>7.623699999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>4.1502</v>
+        <v>27.7876</v>
       </c>
       <c r="X17" t="n">
-        <v>-6.0918</v>
+        <v>-20.1642</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>-27.7886</v>
+        <v>-31.8198</v>
       </c>
       <c r="E18" t="n">
-        <v>-32.2401</v>
+        <v>-25.5921</v>
       </c>
       <c r="F18" t="n">
-        <v>4.4514</v>
+        <v>-6.2279</v>
       </c>
       <c r="G18" t="n">
-        <v>-27.6426</v>
+        <v>-36.0379</v>
       </c>
       <c r="H18" t="n">
-        <v>-14.811</v>
+        <v>-8.1966</v>
       </c>
       <c r="I18" t="n">
-        <v>-12.8317</v>
+        <v>-27.8407</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4691</v>
+        <v>-5.0625</v>
       </c>
       <c r="K18" t="n">
-        <v>-8.5449</v>
+        <v>3.298</v>
       </c>
       <c r="L18" t="n">
-        <v>7.0757</v>
+        <v>-8.360700000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-26.1739</v>
+        <v>-30.9753</v>
       </c>
       <c r="N18" t="n">
-        <v>-6.266100000000001</v>
+        <v>-11.4947</v>
       </c>
       <c r="O18" t="n">
-        <v>-19.9076</v>
+        <v>-19.4806</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.8726</v>
+        <v>17.4004</v>
       </c>
       <c r="Q18" t="n">
-        <v>-49.1565</v>
+        <v>-28.0582</v>
       </c>
       <c r="R18" t="n">
-        <v>43.284</v>
+        <v>45.4586</v>
       </c>
       <c r="S18" t="n">
-        <v>14.6103</v>
+        <v>-7.2989</v>
       </c>
       <c r="T18" t="n">
-        <v>10.8135</v>
+        <v>-3.1146</v>
       </c>
       <c r="U18" t="n">
-        <v>3.7969</v>
+        <v>-4.1843</v>
       </c>
       <c r="V18" t="n">
-        <v>-8.883799999999999</v>
+        <v>-5.884299999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>7.5725</v>
+        <v>10.6429</v>
       </c>
       <c r="X18" t="n">
-        <v>-16.456</v>
+        <v>-16.5272</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>-39.6508</v>
+        <v>-41.2094</v>
       </c>
       <c r="E19" t="n">
-        <v>-31.7175</v>
+        <v>-41.0577</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.933900000000001</v>
+        <v>-0.1511000000000002</v>
       </c>
       <c r="G19" t="n">
-        <v>-36.0379</v>
+        <v>-27.6426</v>
       </c>
       <c r="H19" t="n">
-        <v>-8.1966</v>
+        <v>-14.811</v>
       </c>
       <c r="I19" t="n">
-        <v>-27.8407</v>
+        <v>-12.8317</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.0625</v>
+        <v>-1.4691</v>
       </c>
       <c r="K19" t="n">
-        <v>3.298</v>
+        <v>-8.5449</v>
       </c>
       <c r="L19" t="n">
-        <v>-8.360700000000001</v>
+        <v>7.0757</v>
       </c>
       <c r="M19" t="n">
-        <v>-30.9753</v>
+        <v>-26.1739</v>
       </c>
       <c r="N19" t="n">
-        <v>-11.4947</v>
+        <v>-6.266100000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-19.4806</v>
+        <v>-19.9076</v>
       </c>
       <c r="P19" t="n">
-        <v>17.4004</v>
+        <v>-5.8726</v>
       </c>
       <c r="Q19" t="n">
-        <v>-28.0582</v>
+        <v>-49.1565</v>
       </c>
       <c r="R19" t="n">
-        <v>45.4586</v>
+        <v>43.284</v>
       </c>
       <c r="S19" t="n">
-        <v>-15.1299</v>
+        <v>1.19</v>
       </c>
       <c r="T19" t="n">
-        <v>-9.239599999999999</v>
+        <v>1.995</v>
       </c>
       <c r="U19" t="n">
-        <v>-5.8902</v>
+        <v>-0.8054</v>
       </c>
       <c r="V19" t="n">
-        <v>-5.884299999999999</v>
+        <v>-8.883799999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>10.6429</v>
+        <v>7.5725</v>
       </c>
       <c r="X19" t="n">
-        <v>-16.5272</v>
+        <v>-16.456</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>-70.0262</v>
+        <v>-44.9849</v>
       </c>
       <c r="E20" t="n">
-        <v>-46.2023</v>
+        <v>-29.0063</v>
       </c>
       <c r="F20" t="n">
-        <v>-23.8235</v>
+        <v>-15.9789</v>
       </c>
       <c r="G20" t="n">
         <v>-37.6286</v>
@@ -2014,13 +2014,13 @@
         <v>53.507</v>
       </c>
       <c r="S20" t="n">
-        <v>-42.4582</v>
+        <v>-17.4166</v>
       </c>
       <c r="T20" t="n">
-        <v>-26.3058</v>
+        <v>-9.1098</v>
       </c>
       <c r="U20" t="n">
-        <v>-16.1521</v>
+        <v>-8.3072</v>
       </c>
       <c r="V20" t="n">
         <v>21.3706</v>
@@ -2047,13 +2047,13 @@
         <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>-100.5415</v>
+        <v>-85.19409999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-77.0082</v>
+        <v>-66.2073</v>
       </c>
       <c r="F21" t="n">
-        <v>-23.5334</v>
+        <v>-18.9867</v>
       </c>
       <c r="G21" t="n">
         <v>-61.7369</v>
@@ -2092,13 +2092,13 @@
         <v>45.4592</v>
       </c>
       <c r="S21" t="n">
-        <v>-27.4498</v>
+        <v>-12.1023</v>
       </c>
       <c r="T21" t="n">
-        <v>-16.6452</v>
+        <v>-5.8444</v>
       </c>
       <c r="U21" t="n">
-        <v>-10.8046</v>
+        <v>-6.2574</v>
       </c>
       <c r="V21" t="n">
         <v>8.655800000000001</v>
@@ -2125,13 +2125,13 @@
         <v>32</v>
       </c>
       <c r="D22" t="n">
-        <v>-330.8925</v>
+        <v>-299.2517</v>
       </c>
       <c r="E22" t="n">
-        <v>-227.0375</v>
+        <v>-214.0232</v>
       </c>
       <c r="F22" t="n">
-        <v>-103.8544</v>
+        <v>-85.2289</v>
       </c>
       <c r="G22" t="n">
         <v>-268.535</v>
@@ -2143,13 +2143,13 @@
         <v>-166.5547</v>
       </c>
       <c r="J22" t="n">
-        <v>67.78530000000001</v>
+        <v>67.78529999999999</v>
       </c>
       <c r="K22" t="n">
         <v>18.0977</v>
       </c>
       <c r="L22" t="n">
-        <v>49.6837</v>
+        <v>49.68369999999999</v>
       </c>
       <c r="M22" t="n">
         <v>-336.3199</v>
@@ -2161,7 +2161,7 @@
         <v>-216.2428</v>
       </c>
       <c r="P22" t="n">
-        <v>17.3995</v>
+        <v>17.39950000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>-467.6375</v>
@@ -2170,13 +2170,13 @@
         <v>485.0381</v>
       </c>
       <c r="S22" t="n">
-        <v>-102.842</v>
+        <v>-71.19940000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-38.1382</v>
+        <v>-25.124</v>
       </c>
       <c r="U22" t="n">
-        <v>-64.70400000000001</v>
+        <v>-46.0756</v>
       </c>
       <c r="V22" t="n">
         <v>23.0814</v>
